--- a/data/RWY.MI.xlsx
+++ b/data/RWY.MI.xlsx
@@ -20819,6 +20819,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="890">
+      <c r="A890" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B890" t="n">
+        <v>0</v>
+      </c>
+      <c r="C890" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D890" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E890" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F890" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="G890" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B891" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C891" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D891" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E891" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F891" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="G891" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RWY.MI.xlsx
+++ b/data/RWY.MI.xlsx
@@ -20865,6 +20865,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="892">
+      <c r="A892" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B892" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C892" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D892" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E892" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F892" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="G892" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RWY.MI.xlsx
+++ b/data/RWY.MI.xlsx
@@ -20888,6 +20888,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="893">
+      <c r="A893" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B893" t="n">
+        <v>500</v>
+      </c>
+      <c r="C893" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D893" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E893" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F893" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="G893" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RWY.MI.xlsx
+++ b/data/RWY.MI.xlsx
@@ -20911,6 +20911,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="894">
+      <c r="A894" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B894" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C894" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D894" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E894" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F894" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="G894" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RWY.MI.xlsx
+++ b/data/RWY.MI.xlsx
@@ -20752,10 +20752,10 @@
     </row>
     <row r="887">
       <c r="A887" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B887" t="n">
-        <v>25000</v>
+        <v>1000</v>
       </c>
       <c r="C887" t="n">
         <v>10.1999998092651</v>
@@ -20775,10 +20775,10 @@
     </row>
     <row r="888">
       <c r="A888" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B888" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="C888" t="n">
         <v>10.1999998092651</v>
@@ -20798,10 +20798,10 @@
     </row>
     <row r="889">
       <c r="A889" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B889" t="n">
-        <v>19000</v>
+        <v>0</v>
       </c>
       <c r="C889" t="n">
         <v>10.1999998092651</v>
@@ -20821,10 +20821,10 @@
     </row>
     <row r="890">
       <c r="A890" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B890" t="n">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="C890" t="n">
         <v>10.1999998092651</v>
@@ -20844,10 +20844,10 @@
     </row>
     <row r="891">
       <c r="A891" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B891" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C891" t="n">
         <v>10.1999998092651</v>
@@ -20867,10 +20867,10 @@
     </row>
     <row r="892">
       <c r="A892" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B892" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="C892" t="n">
         <v>10.1999998092651</v>
@@ -20890,10 +20890,10 @@
     </row>
     <row r="893">
       <c r="A893" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B893" t="n">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="C893" t="n">
         <v>10.1999998092651</v>
@@ -20913,10 +20913,10 @@
     </row>
     <row r="894">
       <c r="A894" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B894" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="C894" t="n">
         <v>10.1999998092651</v>
@@ -20931,6 +20931,29 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G894" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B895" t="n">
+        <v>500</v>
+      </c>
+      <c r="C895" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D895" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E895" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F895" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="G895" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RWY.MI.xlsx
+++ b/data/RWY.MI.xlsx
@@ -21003,6 +21003,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="898">
+      <c r="A898" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B898" t="n">
+        <v>0</v>
+      </c>
+      <c r="C898" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D898" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E898" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F898" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="G898" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RWY.MI.xlsx
+++ b/data/RWY.MI.xlsx
@@ -23775,6 +23775,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="901">
+      <c r="A901" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B901" t="n">
+        <v>71000</v>
+      </c>
+      <c r="C901" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D901" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E901" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F901" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="G901" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="H901" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RWY.MI.xlsx
+++ b/data/RWY.MI.xlsx
@@ -23853,6 +23853,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="904">
+      <c r="A904" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B904" t="n">
+        <v>70000</v>
+      </c>
+      <c r="C904" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D904" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E904" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F904" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="G904" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="H904" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RWY.MI.xlsx
+++ b/data/RWY.MI.xlsx
@@ -21226,7 +21226,9 @@
       <c r="E907" t="n">
         <v>10.1999998092651</v>
       </c>
-      <c r="F907"/>
+      <c r="F907" t="n">
+        <v>10.1999998092651</v>
+      </c>
       <c r="G907" t="s">
         <v>7</v>
       </c>

--- a/data/RWY.MI.xlsx
+++ b/data/RWY.MI.xlsx
@@ -21233,6 +21233,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="908">
+      <c r="A908" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B908" t="n">
+        <v>0</v>
+      </c>
+      <c r="C908" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D908" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E908" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F908" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="G908" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B909" t="n">
+        <v>450000</v>
+      </c>
+      <c r="C909" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D909" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E909" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F909"/>
+      <c r="G909" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RWY.MI.xlsx
+++ b/data/RWY.MI.xlsx
@@ -21272,8 +21272,31 @@
       <c r="E909" t="n">
         <v>10.1999998092651</v>
       </c>
-      <c r="F909"/>
+      <c r="F909" t="n">
+        <v>10.1999998092651</v>
+      </c>
       <c r="G909" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B910" t="n">
+        <v>95000</v>
+      </c>
+      <c r="C910" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D910" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E910" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F910"/>
+      <c r="G910" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RWY.MI.xlsx
+++ b/data/RWY.MI.xlsx
@@ -21295,8 +21295,31 @@
       <c r="E910" t="n">
         <v>10.1999998092651</v>
       </c>
-      <c r="F910"/>
+      <c r="F910" t="n">
+        <v>10.1999998092651</v>
+      </c>
       <c r="G910" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B911" t="n">
+        <v>30500</v>
+      </c>
+      <c r="C911" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D911" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E911" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F911"/>
+      <c r="G911" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RWY.MI.xlsx
+++ b/data/RWY.MI.xlsx
@@ -21325,6 +21325,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="912">
+      <c r="A912" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B912" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C912" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D912" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E912" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F912" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="G912" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RWY.MI.xlsx
+++ b/data/RWY.MI.xlsx
@@ -21394,6 +21394,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="915">
+      <c r="A915" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B915" t="n">
+        <v>0</v>
+      </c>
+      <c r="C915" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D915" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E915" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F915" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="G915" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RWY.MI.xlsx
+++ b/data/RWY.MI.xlsx
@@ -26942,6 +26942,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="917">
+      <c r="A917" t="s">
+        <v>9</v>
+      </c>
+      <c r="B917" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C917" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="D917" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="E917" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="F917" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="G917" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="H917" t="n">
+        <v>500</v>
+      </c>
+      <c r="I917" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="s">
+        <v>9</v>
+      </c>
+      <c r="B918" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C918" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D918" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E918" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F918" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="G918" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="H918" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I918" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RWY.MI.xlsx
+++ b/data/RWY.MI.xlsx
@@ -27000,6 +27000,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="919">
+      <c r="A919" t="s">
+        <v>9</v>
+      </c>
+      <c r="B919" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C919" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D919" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E919" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F919" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="G919" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="H919" t="n">
+        <v>0</v>
+      </c>
+      <c r="I919" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RWY.MI.xlsx
+++ b/data/RWY.MI.xlsx
@@ -27029,6 +27029,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="920">
+      <c r="A920" t="s">
+        <v>9</v>
+      </c>
+      <c r="B920" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C920" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D920" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E920" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F920" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="G920" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="H920" t="n">
+        <v>0</v>
+      </c>
+      <c r="I920" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="s">
+        <v>9</v>
+      </c>
+      <c r="B921" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C921" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D921" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E921" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F921" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="G921" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="H921" t="n">
+        <v>500</v>
+      </c>
+      <c r="I921" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RWY.MI.xlsx
+++ b/data/RWY.MI.xlsx
@@ -27087,6 +27087,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="922">
+      <c r="A922" t="s">
+        <v>9</v>
+      </c>
+      <c r="B922" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C922" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D922" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E922" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F922" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="G922" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="H922" t="n">
+        <v>0</v>
+      </c>
+      <c r="I922" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="s">
+        <v>9</v>
+      </c>
+      <c r="B923" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C923" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D923" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E923" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F923" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="G923" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="H923" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I923" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RWY.MI.xlsx
+++ b/data/RWY.MI.xlsx
@@ -27145,6 +27145,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="924">
+      <c r="A924" t="s">
+        <v>9</v>
+      </c>
+      <c r="B924" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C924" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="D924" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="E924" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="F924" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="G924" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="H924" t="n">
+        <v>15500</v>
+      </c>
+      <c r="I924" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RWY.MI.xlsx
+++ b/data/RWY.MI.xlsx
@@ -27174,6 +27174,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="925">
+      <c r="A925" t="s">
+        <v>9</v>
+      </c>
+      <c r="B925" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C925" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="D925" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="E925" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="F925" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="G925" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="H925" t="n">
+        <v>0</v>
+      </c>
+      <c r="I925" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
